--- a/02_DIA_inicio_2026_analisis_assets/rbd_9413_escuela-general-basica-santa-fe_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9413_escuela-general-basica-santa-fe_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2F790E9-D815-4C3B-901F-049094415D86}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{229D76B9-5A54-49C7-A621-DABFA592B18B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0444E3F-3C6A-4E70-81AC-97B06993F4FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0261CAB-8699-47A1-98A0-D738DF4812CC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A5B009E-4004-4DA8-847E-07ED98A8D089}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A476C235-95D9-4D19-8790-143ECF81BDFA}"/>
 </file>